--- a/AAII_Financials/Yearly/VSTS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VSTS_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>VSTS</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,44 +656,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45198</v>
+      </c>
+      <c r="E7" s="2">
         <v>44834</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44470</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44106</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -703,24 +703,27 @@
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2825300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2687000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2456600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2562000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -730,24 +733,27 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1970200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1909700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1765600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1814000</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -757,24 +763,27 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>855100</v>
+      </c>
+      <c r="E10" s="3">
         <v>777300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>690900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>748000</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,9 +793,12 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -798,8 +810,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -824,9 +837,12 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -851,51 +867,57 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>15300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>136500</v>
+      </c>
+      <c r="E15" s="3">
         <v>134400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>133300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>137200</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
@@ -905,9 +927,12 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -916,23 +941,24 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2607400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2494800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2360300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2412300</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
       </c>
@@ -942,24 +968,27 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E18" s="3">
         <v>192200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>96200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>149700</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
@@ -969,9 +998,12 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -983,23 +1015,24 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3700</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,24 +1042,27 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>410400</v>
+      </c>
+      <c r="E21" s="3">
         <v>327500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>234100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>290600</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,24 +1072,27 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E22" s="3">
         <v>3200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3900</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1063,24 +1102,27 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E23" s="3">
         <v>190000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>97400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>149500</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1090,24 +1132,27 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E24" s="3">
         <v>48300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>37900</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1117,9 +1162,12 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1144,24 +1192,27 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>213200</v>
+      </c>
+      <c r="E26" s="3">
         <v>141700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>74300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>111600</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,24 +1222,27 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>213200</v>
+      </c>
+      <c r="E27" s="3">
         <v>141700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>74300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>111600</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1198,9 +1252,12 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1225,9 +1282,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1252,9 +1312,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1279,9 +1342,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1306,24 +1372,27 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3700</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1333,24 +1402,27 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>213200</v>
+      </c>
+      <c r="E33" s="3">
         <v>141700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>74300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>111600</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1360,9 +1432,12 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1387,24 +1462,27 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>213200</v>
+      </c>
+      <c r="E35" s="3">
         <v>141700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>74300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>111600</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1414,29 +1492,32 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45198</v>
+      </c>
+      <c r="E38" s="2">
         <v>44834</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44470</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44106</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1446,9 +1527,12 @@
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1460,8 +1544,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1473,20 +1558,21 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E41" s="3">
         <v>23700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41100</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,9 +1585,12 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1526,21 +1615,24 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>392900</v>
+      </c>
+      <c r="E43" s="3">
         <v>368700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>317300</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1553,21 +1645,24 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E44" s="3">
         <v>183400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>203400</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,21 +1675,24 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>416300</v>
+      </c>
+      <c r="E45" s="3">
         <v>411400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>370100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1607,21 +1705,24 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1020000</v>
+      </c>
+      <c r="E46" s="3">
         <v>987300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>931900</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1634,9 +1735,12 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1661,21 +1765,24 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>722400</v>
+      </c>
+      <c r="E48" s="3">
         <v>722200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>740300</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1688,21 +1795,24 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1202200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1227600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1241800</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1715,9 +1825,12 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1742,9 +1855,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1769,21 +1885,24 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>212600</v>
+      </c>
+      <c r="E52" s="3">
         <v>195900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>194400</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1796,9 +1915,12 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1823,21 +1945,24 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3157100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3133000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3108400</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1850,9 +1975,12 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1864,8 +1992,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1877,20 +2006,21 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>134500</v>
+      </c>
+      <c r="E57" s="3">
         <v>167100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>133400</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,21 +2033,24 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E58" s="3">
         <v>20500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22300</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,21 +2063,24 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>207100</v>
+      </c>
+      <c r="E59" s="3">
         <v>214600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>227700</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,21 +2093,24 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>395500</v>
+      </c>
+      <c r="E60" s="3">
         <v>402200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>383300</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
       </c>
@@ -1984,21 +2123,24 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1567900</v>
+      </c>
+      <c r="E61" s="3">
         <v>86800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>81700</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -2011,21 +2153,24 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>316300</v>
+      </c>
+      <c r="E62" s="3">
         <v>308200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>311400</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2038,9 +2183,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2065,9 +2213,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2092,9 +2243,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2119,21 +2273,24 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2279800</v>
+      </c>
+      <c r="E66" s="3">
         <v>797200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>776400</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2146,9 +2303,12 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2160,8 +2320,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2186,9 +2347,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2213,9 +2377,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2240,9 +2407,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2267,9 +2437,12 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2294,9 +2467,12 @@
       <c r="J72" s="3">
         <v>0</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2321,9 +2497,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2348,9 +2527,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2375,21 +2557,24 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>877400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2335800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2332000</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2402,9 +2587,12 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2429,29 +2617,32 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45198</v>
+      </c>
+      <c r="E80" s="2">
         <v>44834</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44470</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44106</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2461,24 +2652,27 @@
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>213200</v>
+      </c>
+      <c r="E81" s="3">
         <v>141700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>74300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>111600</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,9 +2682,12 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2502,23 +2699,24 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>136500</v>
+      </c>
+      <c r="E83" s="3">
         <v>134400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>133300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>137200</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,9 +2726,12 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2555,9 +2756,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2582,9 +2786,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2609,9 +2816,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2636,9 +2846,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2663,24 +2876,27 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>257000</v>
+      </c>
+      <c r="E89" s="3">
         <v>232800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>244300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>231300</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,9 +2906,12 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2704,23 +2923,24 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-76400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-90100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58100</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
@@ -2730,9 +2950,12 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2757,9 +2980,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2784,24 +3010,27 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-86100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-103200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43400</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,9 +3040,12 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2825,8 +3057,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -2851,9 +3084,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2878,9 +3114,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2905,9 +3144,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2932,24 +3174,27 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-230300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-162500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-125500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-175100</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,24 +3204,27 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -2986,24 +3234,27 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12900</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3013,7 +3264,10 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VSTS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VSTS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>VSTS</t>
   </si>
@@ -656,47 +656,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E7" s="2">
         <v>45198</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44470</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44106</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -706,27 +706,30 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2805800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2825300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2687000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2456600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2562000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -736,26 +739,29 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1989900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1970200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1909700</v>
       </c>
-      <c r="F9" s="3">
-        <v>1765600</v>
-      </c>
       <c r="G9" s="3">
-        <v>1814000</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
+        <v>1745300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1831000</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
@@ -766,26 +772,29 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>815900</v>
+      </c>
+      <c r="E10" s="3">
         <v>855100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>777300</v>
       </c>
-      <c r="F10" s="3">
-        <v>690900</v>
-      </c>
       <c r="G10" s="3">
-        <v>748000</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
+        <v>711200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>731000</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
@@ -796,9 +805,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,8 +823,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -840,9 +853,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -870,26 +886,29 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>15300</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>5200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-51800</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>22600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5900</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -897,42 +916,48 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>140800</v>
+      </c>
+      <c r="E15" s="3">
         <v>136500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>134400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>133300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>137200</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,25 +967,26 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2642600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2607400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2494800</v>
       </c>
-      <c r="F17" s="3">
-        <v>2360300</v>
-      </c>
       <c r="G17" s="3">
-        <v>2412300</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
+        <v>2337700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2406400</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
@@ -971,26 +997,29 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>163200</v>
+      </c>
+      <c r="E18" s="3">
         <v>217900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>192200</v>
       </c>
-      <c r="F18" s="3">
-        <v>96200</v>
-      </c>
       <c r="G18" s="3">
-        <v>149700</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
+        <v>118800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>155600</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
@@ -1001,9 +1030,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1016,22 +1048,23 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>56000</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
-        <v>900</v>
+        <v>-2100</v>
       </c>
       <c r="F20" s="3">
-        <v>4500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>3700</v>
+        <v>-2300</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1045,56 +1078,62 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>410400</v>
+        <v>304600</v>
       </c>
       <c r="E21" s="3">
-        <v>327500</v>
+        <v>356500</v>
       </c>
       <c r="F21" s="3">
-        <v>234100</v>
+        <v>328900</v>
       </c>
       <c r="G21" s="3">
-        <v>290600</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>252100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>292800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E22" s="3">
         <v>4200</v>
       </c>
-      <c r="E22" s="3">
-        <v>3200</v>
-      </c>
       <c r="F22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+        <v>4500</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>200</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1105,27 +1144,30 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E23" s="3">
         <v>269700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>190000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>97400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>149500</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1135,27 +1177,30 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E24" s="3">
         <v>56600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>48300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>23100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>37900</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1165,9 +1210,12 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1195,27 +1243,30 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E26" s="3">
         <v>213200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>141700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>74300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>111600</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,26 +1276,29 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E27" s="3">
         <v>213200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>141700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>74300</v>
       </c>
-      <c r="G27" s="3">
-        <v>111600</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
+      <c r="H27" s="3">
+        <v>111700</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
@@ -1255,9 +1309,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,9 +1342,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1315,9 +1375,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1375,23 +1441,26 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-56000</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
-        <v>-900</v>
+        <v>2100</v>
       </c>
       <c r="F32" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-3700</v>
+        <v>2300</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1405,27 +1474,30 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E33" s="3">
         <v>213200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>141700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>74300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>111600</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,9 +1507,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1465,27 +1540,30 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E35" s="3">
         <v>213200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>141700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>74300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>111600</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,32 +1573,35 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E38" s="2">
         <v>45198</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44470</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44106</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1530,9 +1611,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1559,23 +1644,24 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E41" s="3">
         <v>36100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,9 +1674,12 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1618,24 +1707,27 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>177300</v>
+      </c>
+      <c r="E43" s="3">
         <v>392900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>368700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>317300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1648,23 +1740,26 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>174700</v>
+        <v>561000</v>
       </c>
       <c r="E44" s="3">
-        <v>183400</v>
+        <v>573800</v>
       </c>
       <c r="F44" s="3">
-        <v>203400</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+        <v>576600</v>
+      </c>
+      <c r="G44" s="3">
+        <v>557100</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1678,23 +1773,26 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>416300</v>
+        <v>18100</v>
       </c>
       <c r="E45" s="3">
-        <v>411400</v>
+        <v>17200</v>
       </c>
       <c r="F45" s="3">
-        <v>370100</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+        <v>18300</v>
+      </c>
+      <c r="G45" s="3">
+        <v>16400</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1708,24 +1806,27 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>787400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1020000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>987300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>931900</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,54 +1839,60 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>744400</v>
+      </c>
+      <c r="E48" s="3">
         <v>722400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>722200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>740300</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1798,24 +1905,27 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1176600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1202200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1227600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1241800</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1828,9 +1938,12 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,23 +2004,26 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>212600</v>
+        <v>116600</v>
       </c>
       <c r="E52" s="3">
-        <v>195900</v>
+        <v>108200</v>
       </c>
       <c r="F52" s="3">
-        <v>194400</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+        <v>96900</v>
+      </c>
+      <c r="G52" s="3">
+        <v>98900</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1918,9 +2037,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,24 +2070,27 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2932400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3157100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3133000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3108400</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,9 +2103,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,23 +2136,24 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>163100</v>
+      </c>
+      <c r="E57" s="3">
         <v>134500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>167100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>133400</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,23 +2166,26 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>53900</v>
+        <v>51200</v>
       </c>
       <c r="E58" s="3">
-        <v>20500</v>
+        <v>73800</v>
       </c>
       <c r="F58" s="3">
-        <v>22300</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>41400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>43600</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2066,20 +2199,23 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>207100</v>
-      </c>
-      <c r="E59" s="3">
-        <v>214600</v>
+        <v>4600</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F59" s="3">
-        <v>227700</v>
+        <v>16600</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2096,24 +2232,27 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>456100</v>
+      </c>
+      <c r="E60" s="3">
         <v>395500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>402200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>383300</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2126,23 +2265,26 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1567900</v>
+        <v>1329200</v>
       </c>
       <c r="E61" s="3">
-        <v>86800</v>
+        <v>1614000</v>
       </c>
       <c r="F61" s="3">
-        <v>81700</v>
+        <v>140800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>137900</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2156,23 +2298,26 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>316300</v>
+        <v>52600</v>
       </c>
       <c r="E62" s="3">
-        <v>308200</v>
+        <v>52600</v>
       </c>
       <c r="F62" s="3">
-        <v>311400</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+        <v>52400</v>
+      </c>
+      <c r="G62" s="3">
+        <v>70900</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2186,9 +2331,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,24 +2430,27 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2029300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2279800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>797200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>776400</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2306,9 +2463,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,39 +2610,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+        <v>2600</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3">
+        <v>0</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,24 +2742,27 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>903100</v>
+      </c>
+      <c r="E76" s="3">
         <v>877400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2335800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2332000</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,9 +2775,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,32 +2808,35 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E80" s="2">
         <v>45198</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44470</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44106</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2655,27 +2846,30 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E81" s="3">
         <v>213200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>141700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>74300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>111600</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2685,9 +2879,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,26 +2897,27 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>136500</v>
+        <v>114900</v>
       </c>
       <c r="E83" s="3">
-        <v>134400</v>
+        <v>110500</v>
       </c>
       <c r="F83" s="3">
+        <v>108500</v>
+      </c>
+      <c r="G83" s="3">
         <v>133300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>137200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,9 +2927,12 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,27 +3092,30 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>471800</v>
+      </c>
+      <c r="E89" s="3">
         <v>257000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>232800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>244300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>231300</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -2909,9 +3125,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,26 +3143,27 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-77900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-76400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-90100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58100</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,9 +3173,12 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,27 +3239,30 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-73600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-86100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-103200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-43400</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,9 +3272,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,25 +3290,26 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>1688900</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>134500</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>95600</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>143000</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
@@ -3087,9 +3320,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,27 +3419,30 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-403000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-230300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-162500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-125500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-175100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3207,27 +3452,30 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3237,37 +3485,43 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E102" s="3">
         <v>12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12900</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VSTS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VSTS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>VSTS</t>
   </si>
@@ -656,50 +656,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45933</v>
+      </c>
+      <c r="E7" s="2">
         <v>45562</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45198</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44470</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44106</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -709,30 +710,33 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2734800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2805800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2825300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2687000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2456600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2562000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -742,30 +746,33 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2010100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1989900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1970200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1909700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1745300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1831000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -775,30 +782,33 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>724800</v>
+      </c>
+      <c r="E10" s="3">
         <v>815900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>855100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>777300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>711200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>731000</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,9 +818,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +837,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,9 +870,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,75 +906,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E14" s="3">
         <v>5200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-51800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>22600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E15" s="3">
         <v>140800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>136500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>134400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>133300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>137200</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,29 +994,30 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2651700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2642600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2607400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2494800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2337700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2406400</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,30 +1027,33 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E18" s="3">
         <v>163200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>217900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>192200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>118800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>155600</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1033,9 +1063,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,23 +1082,24 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,63 +1115,69 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>212400</v>
+      </c>
+      <c r="E21" s="3">
         <v>304600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>356500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>328900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>252100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>292800</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E22" s="3">
         <v>122700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4500</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1147,30 +1187,33 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="E23" s="3">
         <v>32000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>269700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>190000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>97400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>149500</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,30 +1223,33 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>11100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>56600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>48300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>23100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37900</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,9 +1259,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,30 +1295,33 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E26" s="3">
         <v>21000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>213200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>141700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>74300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>111600</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1279,30 +1331,33 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E27" s="3">
         <v>21000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>213200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>141700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>74300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>111700</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1312,9 +1367,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1403,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1378,9 +1439,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1475,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,24 +1511,27 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1477,30 +1547,33 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E33" s="3">
         <v>21000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>213200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>141700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>74300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>111600</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,9 +1583,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,30 +1619,33 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E35" s="3">
         <v>21000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>213200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>141700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>74300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>111600</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,35 +1655,38 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45933</v>
+      </c>
+      <c r="E38" s="2">
         <v>45562</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45198</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44470</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44106</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1614,9 +1696,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1715,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,26 +1731,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E41" s="3">
         <v>31000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41100</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,9 +1764,12 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1710,27 +1800,30 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E43" s="3">
         <v>177300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>392900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>368700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>317300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1743,27 +1836,30 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>584600</v>
+      </c>
+      <c r="E44" s="3">
         <v>561000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>573800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>576600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>557100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,27 +1872,30 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18100</v>
+        <v>73300</v>
       </c>
       <c r="E45" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F45" s="3">
         <v>17200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,27 +1908,30 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>787400</v>
+        <v>850000</v>
       </c>
       <c r="E46" s="3">
+        <v>813300</v>
+      </c>
+      <c r="F46" s="3">
         <v>1020000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>987300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>931900</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1842,9 +1944,12 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1869,33 +1974,36 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>748600</v>
+      </c>
+      <c r="E48" s="3">
         <v>744400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>722400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>722200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>740300</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1908,27 +2016,30 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1150600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1176600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1202200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1227600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1241800</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,9 +2052,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2088,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,27 +2124,30 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>116600</v>
+        <v>48800</v>
       </c>
       <c r="E52" s="3">
+        <v>196500</v>
+      </c>
+      <c r="F52" s="3">
         <v>108200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>96900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>98900</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,9 +2160,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,27 +2196,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2906900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2932400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3157100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3133000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3108400</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2106,9 +2232,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2251,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,26 +2267,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>158400</v>
+      </c>
+      <c r="E57" s="3">
         <v>163100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>134500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>167100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>133400</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,27 +2300,30 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E58" s="3">
         <v>51200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>73800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>41400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>43600</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,24 +2336,27 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
         <v>16600</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,27 +2372,30 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E60" s="3">
         <v>456100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>395500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>402200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>383300</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2268,27 +2408,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1363200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1329200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1614000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>140800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>137900</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2301,27 +2444,30 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>52600</v>
+        <v>91700</v>
       </c>
       <c r="E62" s="3">
         <v>52600</v>
       </c>
       <c r="F62" s="3">
+        <v>52600</v>
+      </c>
+      <c r="G62" s="3">
         <v>52400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>70900</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2334,9 +2480,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2516,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2552,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,27 +2588,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2041300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2029300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2279800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>797200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>776400</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,9 +2624,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2643,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2676,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2712,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2748,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,18 +2784,21 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="E72" s="3">
         <v>2600</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2640,15 +2814,18 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2856,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2892,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,27 +2928,30 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>865600</v>
+      </c>
+      <c r="E76" s="3">
         <v>903100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>877400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2335800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2332000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,9 +2964,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,35 +3000,38 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45933</v>
+      </c>
+      <c r="E80" s="2">
         <v>45562</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45198</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44470</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44106</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2849,30 +3041,33 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E81" s="3">
         <v>21000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>213200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>141700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>74300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>111600</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2882,9 +3077,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,29 +3096,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>115900</v>
+      </c>
+      <c r="E83" s="3">
         <v>114900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>110500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>108500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>133300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>137200</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,9 +3129,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3165,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3201,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3237,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3273,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,30 +3309,33 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E89" s="3">
         <v>471800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>257000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>232800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>244300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>231300</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,9 +3345,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,29 +3364,30 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-78900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-77900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-76400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-90100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58100</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,9 +3397,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3433,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,30 +3469,33 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-73600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-86100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-103200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-43400</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3505,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,29 +3524,30 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E96" s="3">
         <v>19900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1688900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>134500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>95600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>143000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -3323,9 +3557,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3593,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3629,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,30 +3665,33 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-46100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-403000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-230300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-162500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-125500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-175100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,30 +3701,33 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3488,40 +3737,46 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12900</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
